--- a/bench/corpus/clean-01.xlsx
+++ b/bench/corpus/clean-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyank\Desktop\後藤さんのclaude\ai-builders-2026\gridlint\bench\corpus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12BFB750-F0ED-4E4A-906A-9CE377336251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B4E9827-9C7E-44C7-95AB-B35BBBEC8069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F201BCDC-6F81-47C3-B252-3D53038E7974}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1616085-628E-479F-9FC4-3948003EB58E}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Assumption</t>
   </si>
@@ -78,6 +78,24 @@
     <t>Jun</t>
   </si>
   <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
     <t>REVENUE</t>
   </si>
   <si>
@@ -123,30 +141,6 @@
     <t>Grand total</t>
   </si>
   <si>
-    <t>Share of first month</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>North</t>
-  </si>
-  <si>
-    <t>South</t>
-  </si>
-  <si>
-    <t>East</t>
-  </si>
-  <si>
-    <t>West</t>
-  </si>
-  <si>
-    <t>Weighted first month</t>
-  </si>
-  <si>
     <t>Full year</t>
   </si>
   <si>
@@ -154,6 +148,9 @@
   </si>
   <si>
     <t>Months of cash</t>
+  </si>
+  <si>
+    <t>helper</t>
   </si>
 </sst>
 </file>
@@ -546,22 +543,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779D970D-6E59-4096-B7BC-BFD5D4A242A7}">
-  <dimension ref="A1:H33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C41C96-CC8E-4BC7-B3E7-3F26B410AA03}">
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.625" customWidth="1"/>
     <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -583,15 +581,44 @@
       <c r="H3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="P4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2">
         <v>7.0999999999999994E-2</v>
@@ -619,10 +646,37 @@
         <f>G6*(1+$B$6)</f>
         <v>187412.69036036864</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I6" s="1">
+        <f>H6*(1+$B$6)</f>
+        <v>200718.99137595479</v>
+      </c>
+      <c r="J6" s="1">
+        <f>I6*(1+$B$6)</f>
+        <v>214970.03976364757</v>
+      </c>
+      <c r="K6" s="1">
+        <f>J6*(1+$B$6)</f>
+        <v>230232.91258686653</v>
+      </c>
+      <c r="L6" s="1">
+        <f>K6*(1+$B$6)</f>
+        <v>246579.44938053403</v>
+      </c>
+      <c r="M6" s="1">
+        <f>L6*(1+$B$6)</f>
+        <v>264086.59028655192</v>
+      </c>
+      <c r="N6" s="1">
+        <f>M6*(1+$B$6)</f>
+        <v>282836.73819689709</v>
+      </c>
+      <c r="P6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2">
         <v>6.9000000000000006E-2</v>
@@ -650,10 +704,37 @@
         <f>G7*(1+$B$7)</f>
         <v>323874.31759563286</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I7" s="1">
+        <f>H7*(1+$B$7)</f>
+        <v>346221.64550973149</v>
+      </c>
+      <c r="J7" s="1">
+        <f>I7*(1+$B$7)</f>
+        <v>370110.93904990295</v>
+      </c>
+      <c r="K7" s="1">
+        <f>J7*(1+$B$7)</f>
+        <v>395648.59384434624</v>
+      </c>
+      <c r="L7" s="1">
+        <f>K7*(1+$B$7)</f>
+        <v>422948.34681960609</v>
+      </c>
+      <c r="M7" s="1">
+        <f>L7*(1+$B$7)</f>
+        <v>452131.78275015886</v>
+      </c>
+      <c r="N7" s="1">
+        <f>M7*(1+$B$7)</f>
+        <v>483328.87575991981</v>
+      </c>
+      <c r="P7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2">
         <v>5.0999999999999997E-2</v>
@@ -681,10 +762,34 @@
         <f>G8*(1+$B$8)</f>
         <v>78224.611542845305</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I8" s="1">
+        <f>H8*(1+$B$8)</f>
+        <v>82214.066731530416</v>
+      </c>
+      <c r="J8" s="1">
+        <f>I8*(1+$B$8)</f>
+        <v>86406.984134838465</v>
+      </c>
+      <c r="K8" s="1">
+        <f>J8*(1+$B$8)</f>
+        <v>90813.740325715218</v>
+      </c>
+      <c r="L8" s="1">
+        <f>K8*(1+$B$8)</f>
+        <v>95445.241082326684</v>
+      </c>
+      <c r="M8" s="1">
+        <f>L8*(1+$B$8)</f>
+        <v>100312.94837752533</v>
+      </c>
+      <c r="N8" s="1">
+        <f>M8*(1+$B$8)</f>
+        <v>105428.90874477912</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2">
         <v>-2E-3</v>
@@ -712,10 +817,34 @@
         <f>G9*(1+$B$9)</f>
         <v>130685.26945055577</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I9" s="1">
+        <f>H9*(1+$B$9)</f>
+        <v>130423.89891165466</v>
+      </c>
+      <c r="J9" s="1">
+        <f>I9*(1+$B$9)</f>
+        <v>130163.05111383134</v>
+      </c>
+      <c r="K9" s="1">
+        <f>J9*(1+$B$9)</f>
+        <v>129902.72501160369</v>
+      </c>
+      <c r="L9" s="1">
+        <f>K9*(1+$B$9)</f>
+        <v>129642.91956158048</v>
+      </c>
+      <c r="M9" s="1">
+        <f>L9*(1+$B$9)</f>
+        <v>129383.63372245732</v>
+      </c>
+      <c r="N9" s="1">
+        <f>M9*(1+$B$9)</f>
+        <v>129124.86645501241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B10" s="2">
         <v>0.09</v>
@@ -743,10 +872,34 @@
         <f>G10*(1+$B$10)</f>
         <v>350806.26171720016</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I10" s="1">
+        <f>H10*(1+$B$10)</f>
+        <v>382378.82527174818</v>
+      </c>
+      <c r="J10" s="1">
+        <f>I10*(1+$B$10)</f>
+        <v>416792.91954620555</v>
+      </c>
+      <c r="K10" s="1">
+        <f>J10*(1+$B$10)</f>
+        <v>454304.28230536409</v>
+      </c>
+      <c r="L10" s="1">
+        <f>K10*(1+$B$10)</f>
+        <v>495191.66771284689</v>
+      </c>
+      <c r="M10" s="1">
+        <f>L10*(1+$B$10)</f>
+        <v>539758.91780700313</v>
+      </c>
+      <c r="N10" s="1">
+        <f>M10*(1+$B$10)</f>
+        <v>588337.22040963348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1">
         <f>SUM(C6:C10)</f>
@@ -772,15 +925,39 @@
         <f>SUM(H6:H10)</f>
         <v>1071003.1506666029</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I11" s="1">
+        <f>SUM(I6:I10)</f>
+        <v>1141957.4278006197</v>
+      </c>
+      <c r="J11" s="1">
+        <f>SUM(J6:J10)</f>
+        <v>1218443.9336084258</v>
+      </c>
+      <c r="K11" s="1">
+        <f>SUM(K6:K10)</f>
+        <v>1300902.2540738957</v>
+      </c>
+      <c r="L11" s="1">
+        <f>SUM(L6:L10)</f>
+        <v>1389807.6245568944</v>
+      </c>
+      <c r="M11" s="1">
+        <f>SUM(M6:M10)</f>
+        <v>1485673.8729436966</v>
+      </c>
+      <c r="N11" s="1">
+        <f>SUM(N6:N10)</f>
+        <v>1589056.609566242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2">
         <v>1.7000000000000001E-2</v>
@@ -808,10 +985,34 @@
         <f>G14*(1+$B$14)</f>
         <v>288303.98049158702</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I14" s="1">
+        <f>H14*(1+$B$14)</f>
+        <v>293205.14815994399</v>
+      </c>
+      <c r="J14" s="1">
+        <f>I14*(1+$B$14)</f>
+        <v>298189.63567866303</v>
+      </c>
+      <c r="K14" s="1">
+        <f>J14*(1+$B$14)</f>
+        <v>303258.85948520026</v>
+      </c>
+      <c r="L14" s="1">
+        <f>K14*(1+$B$14)</f>
+        <v>308414.26009644865</v>
+      </c>
+      <c r="M14" s="1">
+        <f>L14*(1+$B$14)</f>
+        <v>313657.30251808825</v>
+      </c>
+      <c r="N14" s="1">
+        <f>M14*(1+$B$14)</f>
+        <v>318989.47666089574</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2">
         <v>6.7000000000000004E-2</v>
@@ -839,10 +1040,34 @@
         <f>G15*(1+$B$15)</f>
         <v>439793.91596217395</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I15" s="1">
+        <f>H15*(1+$B$15)</f>
+        <v>469260.10833163961</v>
+      </c>
+      <c r="J15" s="1">
+        <f>I15*(1+$B$15)</f>
+        <v>500700.53558985941</v>
+      </c>
+      <c r="K15" s="1">
+        <f>J15*(1+$B$15)</f>
+        <v>534247.47147438</v>
+      </c>
+      <c r="L15" s="1">
+        <f>K15*(1+$B$15)</f>
+        <v>570042.05206316349</v>
+      </c>
+      <c r="M15" s="1">
+        <f>L15*(1+$B$15)</f>
+        <v>608234.86955139542</v>
+      </c>
+      <c r="N15" s="1">
+        <f>M15*(1+$B$15)</f>
+        <v>648986.60581133887</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2">
         <v>-5.0000000000000001E-3</v>
@@ -870,10 +1095,34 @@
         <f>G16*(1+$B$16)</f>
         <v>9752.4875312187505</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I16" s="1">
+        <f>H16*(1+$B$16)</f>
+        <v>9703.7250935626562</v>
+      </c>
+      <c r="J16" s="1">
+        <f>I16*(1+$B$16)</f>
+        <v>9655.2064680948424</v>
+      </c>
+      <c r="K16" s="1">
+        <f>J16*(1+$B$16)</f>
+        <v>9606.9304357543679</v>
+      </c>
+      <c r="L16" s="1">
+        <f>K16*(1+$B$16)</f>
+        <v>9558.8957835755955</v>
+      </c>
+      <c r="M16" s="1">
+        <f>L16*(1+$B$16)</f>
+        <v>9511.1013046577173</v>
+      </c>
+      <c r="N16" s="1">
+        <f>M16*(1+$B$16)</f>
+        <v>9463.545798134428</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2">
         <v>-8.0000000000000002E-3</v>
@@ -901,10 +1150,34 @@
         <f>G17*(1+$B$17)</f>
         <v>282426.66073148622</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I17" s="1">
+        <f>H17*(1+$B$17)</f>
+        <v>280167.24744563433</v>
+      </c>
+      <c r="J17" s="1">
+        <f>I17*(1+$B$17)</f>
+        <v>277925.90946606925</v>
+      </c>
+      <c r="K17" s="1">
+        <f>J17*(1+$B$17)</f>
+        <v>275702.50219034072</v>
+      </c>
+      <c r="L17" s="1">
+        <f>K17*(1+$B$17)</f>
+        <v>273496.882172818</v>
+      </c>
+      <c r="M17" s="1">
+        <f>L17*(1+$B$17)</f>
+        <v>271308.90711543546</v>
+      </c>
+      <c r="N17" s="1">
+        <f>M17*(1+$B$17)</f>
+        <v>269138.43585851195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2">
         <v>6.8000000000000005E-2</v>
@@ -932,10 +1205,34 @@
         <f>G18*(1+$B$18)</f>
         <v>458532.58466847759</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I18" s="1">
+        <f>H18*(1+$B$18)</f>
+        <v>489712.80042593408</v>
+      </c>
+      <c r="J18" s="1">
+        <f>I18*(1+$B$18)</f>
+        <v>523013.27085489762</v>
+      </c>
+      <c r="K18" s="1">
+        <f>J18*(1+$B$18)</f>
+        <v>558578.17327303067</v>
+      </c>
+      <c r="L18" s="1">
+        <f>K18*(1+$B$18)</f>
+        <v>596561.48905559676</v>
+      </c>
+      <c r="M18" s="1">
+        <f>L18*(1+$B$18)</f>
+        <v>637127.67031137738</v>
+      </c>
+      <c r="N18" s="1">
+        <f>M18*(1+$B$18)</f>
+        <v>680452.35189255106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C19" s="1">
         <f>SUM(C14:C18)</f>
@@ -961,10 +1258,34 @@
         <f>SUM(H14:H18)</f>
         <v>1478809.6293849435</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I19" s="1">
+        <f>SUM(I14:I18)</f>
+        <v>1542049.0294567146</v>
+      </c>
+      <c r="J19" s="1">
+        <f>SUM(J14:J18)</f>
+        <v>1609484.5580575841</v>
+      </c>
+      <c r="K19" s="1">
+        <f>SUM(K14:K18)</f>
+        <v>1681393.9368587059</v>
+      </c>
+      <c r="L19" s="1">
+        <f>SUM(L14:L18)</f>
+        <v>1758073.5791716024</v>
+      </c>
+      <c r="M19" s="1">
+        <f>SUM(M14:M18)</f>
+        <v>1839839.8508009543</v>
+      </c>
+      <c r="N19" s="1">
+        <f>SUM(N14:N18)</f>
+        <v>1927030.4160214318</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C21" s="1">
         <f>SUM(C11,C19)</f>
@@ -990,109 +1311,55 @@
         <f>SUM(H11,H19)</f>
         <v>2549812.7800515462</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="2">
-        <f>C21/$C$21</f>
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <f>D21/$C$21</f>
-        <v>1.0472626060908636</v>
-      </c>
-      <c r="E22" s="2">
-        <f>E21/$C$21</f>
-        <v>1.0979351308037941</v>
-      </c>
-      <c r="F22" s="2">
-        <f>F21/$C$21</f>
-        <v>1.1522665378267598</v>
-      </c>
-      <c r="G22" s="2">
-        <f>G21/$C$21</f>
-        <v>1.2105245115362533</v>
-      </c>
-      <c r="H22" s="2">
-        <f>H21/$C$21</f>
-        <v>1.2729968946837475</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I21" s="1">
+        <f>SUM(I11,I19)</f>
+        <v>2684006.4572573341</v>
+      </c>
+      <c r="J21" s="1">
+        <f>SUM(J11,J19)</f>
+        <v>2827928.4916660096</v>
+      </c>
+      <c r="K21" s="1">
+        <f>SUM(K11,K19)</f>
+        <v>2982296.1909326017</v>
+      </c>
+      <c r="L21" s="1">
+        <f>SUM(L11,L19)</f>
+        <v>3147881.203728497</v>
+      </c>
+      <c r="M21" s="1">
+        <f>SUM(M11,M19)</f>
+        <v>3325513.7237446508</v>
+      </c>
+      <c r="N21" s="1">
+        <f>SUM(N11,N19)</f>
+        <v>3516087.0255876738</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="1">
+        <f>SUM(C21:N21)</f>
+        <v>32066027.411842428</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+      <c r="C24" s="1">
+        <f>ROUND(C23/Assumptions!B2,0)</f>
+        <v>337537</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="1">
-        <f>ROUND(C21*VLOOKUP("East",A25:B28,2,FALSE),0)</f>
-        <v>1001500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="1">
-        <f>SUM(C21:H21)</f>
-        <v>13582314.318925662</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="1">
-        <f>ROUND(C31/Assumptions!B2,0)</f>
-        <v>411585</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33">
-        <f>ROUND(Assumptions!B3/AVERAGE(C21:H21),1)</f>
+      <c r="C25">
+        <f>ROUND(Assumptions!B3/AVERAGE(C21:N21),1)</f>
         <v>2.1</v>
       </c>
     </row>
@@ -1103,7 +1370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B5DDCD-2C80-49DE-9D02-1A1A180D361C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3847B392-468A-4726-A9C6-53ADD0B5CB8F}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1123,7 +1390,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>33</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -1131,7 +1398,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>4800000</v>
+        <v>5600000</v>
       </c>
     </row>
   </sheetData>
